--- a/plots/experiment9_compas_queries.xlsx
+++ b/plots/experiment9_compas_queries.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,12 +424,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>age_cat</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>avg-decile_score</t>
         </is>
@@ -454,7 +442,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.76561463040721</v>
+        <v>4.81072410628709</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +452,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.636305093416095</v>
+        <v>3.446238557626496</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +462,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.201452399267086</v>
+        <v>4.745311154675846</v>
       </c>
     </row>
     <row r="8">
@@ -485,12 +473,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>race</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>avg-decile_score</t>
         </is>
@@ -503,7 +491,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.181918469747628</v>
+        <v>5.726451668086566</v>
       </c>
     </row>
     <row r="11">
@@ -513,7 +501,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.036526181353767</v>
+        <v>3.680606070234578</v>
       </c>
     </row>
     <row r="12">
@@ -523,7 +511,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.836056079604686</v>
+        <v>4.637405098980018</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +521,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.467412010159651</v>
+        <v>3.654048456934409</v>
       </c>
     </row>
     <row r="14">
@@ -543,7 +531,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.714492753623188</v>
+        <v>5.306177278537344</v>
       </c>
     </row>
     <row r="15">
@@ -553,7 +541,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.970338751691859</v>
+        <v>3.162309538604558</v>
       </c>
     </row>
     <row r="18">
@@ -564,12 +552,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>race</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>med-decile_score</t>
         </is>
@@ -582,7 +570,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>12.71599850727694</v>
       </c>
     </row>
     <row r="21">
@@ -592,7 +580,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>-0.4554619381272506</v>
       </c>
     </row>
     <row r="22">
@@ -602,7 +590,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3.782425129331953</v>
       </c>
     </row>
     <row r="23">
@@ -612,7 +600,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1.123860682233642</v>
       </c>
     </row>
     <row r="24">
@@ -622,7 +610,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>0.3524146954339185</v>
       </c>
     </row>
     <row r="25">
@@ -632,7 +620,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>-1.522239084734627</v>
       </c>
     </row>
     <row r="28">
@@ -643,12 +631,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>c_charge_degree</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>med-decile_score</t>
         </is>
@@ -661,7 +649,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.5</v>
+        <v>-0.9830879322894376</v>
       </c>
     </row>
     <row r="31">
@@ -671,7 +659,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>4.990588276893751</v>
       </c>
     </row>
     <row r="32">
@@ -681,7 +669,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.25</v>
+        <v>-2.754395857168849</v>
       </c>
     </row>
   </sheetData>
